--- a/data/trans_dic/P37A$medicootras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicootras-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,1</t>
+          <t>0,18; 1,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,36</t>
+          <t>0,13; 1,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,36</t>
+          <t>0,57; 2,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,61</t>
+          <t>0,07; 0,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,26</t>
+          <t>0,26; 1,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,4</t>
+          <t>0,46; 1,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,5</t>
+          <t>0,08; 0,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,94</t>
+          <t>0,24; 0,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,01</t>
+          <t>0,28; 1,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,57</t>
+          <t>0,66; 1,67</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,03</t>
+          <t>0,26; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,06</t>
+          <t>0,31; 1,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,02</t>
+          <t>0,25; 1,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,42</t>
+          <t>0,46; 1,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,99</t>
+          <t>0,3; 0,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,67</t>
+          <t>1,0; 1,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,33</t>
+          <t>0,06; 0,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,02</t>
+          <t>0,43; 1,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,86</t>
+          <t>0,37; 0,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,16</t>
+          <t>0,7; 1,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,88</t>
+          <t>0,16; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,01</t>
+          <t>0,17; 2,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,38</t>
+          <t>0,18; 1,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,54</t>
+          <t>0,22; 2,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,44</t>
+          <t>0,35; 2,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,64</t>
+          <t>0,84; 2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,19</t>
+          <t>0,17; 1,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,54</t>
+          <t>0,29; 1,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,65</t>
+          <t>0,33; 1,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,7</t>
+          <t>0,63; 1,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,44</t>
+          <t>0,09; 0,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,81</t>
+          <t>0,29; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,94</t>
+          <t>0,38; 0,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,01</t>
+          <t>0,41; 0,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,45</t>
+          <t>0,1; 0,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,09</t>
+          <t>0,49; 1,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,99</t>
+          <t>0,41; 0,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,55</t>
+          <t>1,01; 1,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,37</t>
+          <t>0,13; 0,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,84</t>
+          <t>0,42; 0,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,86</t>
+          <t>0,46; 0,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,16</t>
+          <t>0,8; 1,24</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12279</t>
+          <t>14977</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6067</t>
+          <t>0; 6779</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1866; 10676</t>
+          <t>1764; 11699</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>984; 10295</t>
+          <t>972; 9691</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2364; 12135</t>
+          <t>3291; 14407</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>955; 8035</t>
+          <t>956; 8089</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2246; 12925</t>
+          <t>2263; 13022</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2150; 12500</t>
+          <t>2552; 13034</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3094; 10553</t>
+          <t>3746; 12341</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1913; 11702</t>
+          <t>1901; 10832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5975; 21642</t>
+          <t>5634; 20078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4968; 17619</t>
+          <t>4843; 18841</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7459; 19936</t>
+          <t>9255; 23349</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>42012</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5623</t>
+          <t>0; 6874</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5117; 20306</t>
+          <t>5135; 19384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6644; 22062</t>
+          <t>6400; 21142</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4883; 23384</t>
+          <t>5571; 22664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>973; 7961</t>
+          <t>975; 7960</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8911; 25035</t>
+          <t>8119; 24613</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5830; 19658</t>
+          <t>5873; 19481</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17592; 37458</t>
+          <t>21821; 42153</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1871; 10868</t>
+          <t>1874; 10462</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16111; 37781</t>
+          <t>15906; 37759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15784; 34786</t>
+          <t>15223; 36552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25907; 52564</t>
+          <t>30924; 56874</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15335</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>913; 10368</t>
+          <t>904; 11606</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 9616</t>
+          <t>0; 11841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>985; 10984</t>
+          <t>903; 12011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1267; 8932</t>
+          <t>1248; 9339</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6210</t>
+          <t>0; 6189</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>986; 11665</t>
+          <t>995; 11404</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1850; 13388</t>
+          <t>1911; 13015</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5785; 17440</t>
+          <t>6182; 18798</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1223; 12198</t>
+          <t>1701; 13535</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1934; 14492</t>
+          <t>2692; 15650</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3803; 18074</t>
+          <t>3665; 18994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8576; 22197</t>
+          <t>9057; 23355</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>72324</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2907; 14457</t>
+          <t>2979; 14692</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9946; 27683</t>
+          <t>9812; 27024</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12703; 31595</t>
+          <t>12776; 32660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13037; 34692</t>
+          <t>14454; 34720</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3235; 15080</t>
+          <t>3238; 14612</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16982; 38674</t>
+          <t>17284; 39354</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14581; 34871</t>
+          <t>14571; 34511</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32131; 56752</t>
+          <t>37814; 61735</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8652; 24923</t>
+          <t>8863; 25425</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30811; 58261</t>
+          <t>29072; 58383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31701; 59192</t>
+          <t>31490; 58389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51132; 82637</t>
+          <t>57661; 90050</t>
         </is>
       </c>
     </row>
